--- a/results/pr_AstroSync/exp/15AZ/cv_scores/fair_cv_summary.xlsx
+++ b/results/pr_AstroSync/exp/15AZ/cv_scores/fair_cv_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,12 +625,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -658,10 +658,10 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.340106848977012e-10</v>
+        <v>1.833688142873094e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>4.077313062077252e-06</v>
+        <v>2.955709246762203e-06</v>
       </c>
     </row>
     <row r="5">
@@ -682,12 +682,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -715,10 +715,10 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.235916038831386e-09</v>
+        <v>3.135235767890596e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>1.004969431389746e-05</v>
+        <v>4.342365253301594e-06</v>
       </c>
     </row>
     <row r="6">
@@ -739,12 +739,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -772,10 +772,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.207250840133354e-09</v>
+        <v>3.340106848977012e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>1.210274062577692e-05</v>
+        <v>4.077313062077252e-06</v>
       </c>
     </row>
     <row r="7">
@@ -801,7 +801,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -829,10 +829,10 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.658643892074573e-08</v>
+        <v>1.235916038831386e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.746265937158774e-05</v>
+        <v>1.004969431389746e-05</v>
       </c>
     </row>
     <row r="8">
@@ -853,12 +853,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -886,10 +886,10 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.073671711747983e-07</v>
+        <v>3.207250840133354e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>7.376540127924457e-05</v>
+        <v>1.210274062577692e-05</v>
       </c>
     </row>
     <row r="9">
@@ -910,12 +910,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -943,10 +943,10 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.782004461303588e-07</v>
+        <v>4.827014618181592e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>8.82444911994701e-05</v>
+        <v>1.837360102424187e-05</v>
       </c>
     </row>
     <row r="10">
@@ -967,12 +967,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1000,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.724761575514432e-07</v>
+        <v>1.658643892074573e-08</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0001235322186316074</v>
+        <v>2.746265937158774e-05</v>
       </c>
     </row>
     <row r="11">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1057,10 +1057,10 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000979473995336e-06</v>
+        <v>7.17684017884797e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0002131231868360398</v>
+        <v>4.952980976600864e-05</v>
       </c>
     </row>
     <row r="12">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1114,10 +1114,10 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.514780554911556e-06</v>
+        <v>1.073671711747983e-07</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0002278251106338774</v>
+        <v>7.376540127924457e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1171,10 +1171,10 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>9.615603465056026e-06</v>
+        <v>1.782004461303588e-07</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0005710385565825482</v>
+        <v>8.82444911994701e-05</v>
       </c>
     </row>
     <row r="14">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1228,10 +1228,10 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.35171096921186e-05</v>
+        <v>2.724761575514432e-07</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0007113203062599211</v>
+        <v>0.0001235322186316074</v>
       </c>
     </row>
     <row r="15">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1285,10 +1285,10 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.049962139241223e-05</v>
+        <v>3.477192693527149e-07</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0008387559727284656</v>
+        <v>0.0001125281780552315</v>
       </c>
     </row>
     <row r="16">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1342,10 +1342,10 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0001684529126255578</v>
+        <v>4.173887549963946e-07</v>
       </c>
       <c r="O16" t="n">
-        <v>0.002487587631386067</v>
+        <v>0.0001615747076964363</v>
       </c>
     </row>
     <row r="17">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1399,10 +1399,10 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0006072481599660005</v>
+        <v>1.000979473995336e-06</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0048344610728393</v>
+        <v>0.0002131231868360398</v>
       </c>
     </row>
     <row r="18">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01313809090607113</v>
+        <v>1.514780554911556e-06</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06417676495540124</v>
+        <v>0.0002278251106338774</v>
       </c>
     </row>
     <row r="19">
@@ -1485,38 +1485,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0577350269189626</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9696969696969697</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9444444444444445</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9866666666666667</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03576110744625465</v>
+        <v>9.615603465056026e-06</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2958716427381446</v>
+        <v>0.0005710385565825482</v>
       </c>
     </row>
     <row r="20">
@@ -1542,38 +1542,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1154700538379251</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9866666666666667</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.04385853081310775</v>
+        <v>1.35171096921186e-05</v>
       </c>
       <c r="O20" t="n">
-        <v>0.133797875407014</v>
+        <v>0.0007113203062599211</v>
       </c>
     </row>
     <row r="21">
@@ -1594,42 +1594,498 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.721705002722738e-05</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0008287119034914459</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15AZ</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>im_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.049962139241223e-05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0008387559727284656</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15AZ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>im_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.0001684529126255578</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.002487587631386067</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15AZ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>im_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.0006072481599660005</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.0048344610728393</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15AZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>im_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.01313809090607113</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.06417676495540124</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15AZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>im_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>[10, 14]</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0577350269189626</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.9444444444444445</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.03333213244921932</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.3641466995515064</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15AZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>im_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>(0, 1)</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0577350269189626</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.9444444444444445</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.9866666666666667</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.03576110744625465</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.2958716427381446</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15AZ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>im_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1154700538379251</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.9866666666666667</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.04385853081310775</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.133797875407014</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15AZ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>im_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.9</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H29" t="n">
         <v>0.09999999999999998</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I29" t="n">
         <v>0.9</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J29" t="n">
         <v>0.903030303030303</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K29" t="n">
         <v>0.9333333333333332</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L29" t="n">
         <v>0.8777777777777778</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M29" t="n">
         <v>0.9466666666666667</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N29" t="n">
         <v>0.09104060599966098</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O29" t="n">
         <v>0.3666722068169179</v>
       </c>
     </row>
